--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5091,7 +5091,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>175</v>
       </c>
@@ -5106,13 +5106,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5194,7 +5194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>179</v>
       </c>
@@ -5209,13 +5209,13 @@
         <v>180</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5503,7 +5503,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>193</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="337">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -827,6 +827,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7331,7 +7335,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7339,10 +7343,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7368,10 +7372,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7402,7 +7406,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7420,7 +7424,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7440,10 +7444,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7541,10 +7545,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7585,7 +7589,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7644,10 +7648,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7747,10 +7751,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7850,10 +7854,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7953,10 +7957,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8056,10 +8060,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8157,10 +8161,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8258,10 +8262,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8361,10 +8365,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8464,10 +8468,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8567,10 +8571,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8593,7 +8597,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8646,7 +8650,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8666,10 +8670,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8692,7 +8696,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8725,7 +8729,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8743,7 +8747,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8763,10 +8767,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8789,7 +8793,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8842,7 +8846,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8862,10 +8866,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8921,25 +8925,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8959,10 +8963,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8985,7 +8989,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>196</v>
@@ -9022,25 +9026,25 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9060,10 +9064,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9086,7 +9090,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9119,25 +9123,25 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9157,10 +9161,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9183,7 +9187,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9216,25 +9220,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9254,10 +9258,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9284,7 +9288,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9335,7 +9339,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9355,10 +9359,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9381,7 +9385,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9434,7 +9438,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9454,10 +9458,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9480,7 +9484,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9533,7 +9537,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9553,10 +9557,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9579,7 +9583,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9632,7 +9636,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9652,10 +9656,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9678,7 +9682,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9731,7 +9735,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9751,10 +9755,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9777,7 +9781,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9830,7 +9834,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9850,10 +9854,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9876,7 +9880,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9929,7 +9933,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9949,10 +9953,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9975,7 +9979,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10028,7 +10032,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10048,10 +10052,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10074,7 +10078,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10127,7 +10131,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10147,10 +10151,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10173,7 +10177,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10226,7 +10230,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10246,10 +10250,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10272,7 +10276,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10325,7 +10329,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10345,10 +10349,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10371,11 +10375,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10426,7 +10430,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10446,10 +10450,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10547,10 +10551,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10648,10 +10652,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10749,10 +10753,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10850,10 +10854,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10953,10 +10957,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11056,10 +11060,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11159,10 +11163,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11262,10 +11266,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11363,10 +11367,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11400,7 +11404,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>74</v>
@@ -11422,7 +11426,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11440,7 +11444,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11460,10 +11464,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11486,7 +11490,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11539,7 +11543,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -11559,10 +11563,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11585,7 +11589,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11638,7 +11642,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-statut-clinique-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
